--- a/data.xlsx
+++ b/data.xlsx
@@ -606,12 +606,12 @@
       </c>
       <c r="B2" s="31" t="inlineStr">
         <is>
-          <t>連續忙了兩個禮拜，你終於排到幾天假。晚上躺在床上滑手機，看到一篇貼文的照片，突然覺得「這次一定要出去走走」。你覺得那張照片是什麼？</t>
+          <t>連續忙了兩個禮拜，你終於排到幾天假。晚上躺在床上滑手機，滑到一則短影音，突然讓你覺得「好想出去走走」。你覺得那則短影音是什麼？</t>
         </is>
       </c>
       <c r="C2" s="29" t="inlineStr">
         <is>
-          <t>一張退潮後的沙灘照片，整片都是被浪梳過的紋路</t>
+          <t>一段空拍退潮沙灘的短影音，浪一波波把沙紋刷過去</t>
         </is>
       </c>
       <c r="D2" s="29" t="inlineStr">
@@ -645,7 +645,7 @@
     <row r="3" ht="15.75" customHeight="1" s="28">
       <c r="C3" s="29" t="inlineStr">
         <is>
-          <t>一張深夜巷口的照片，燈還亮著，有人坐在騎樓吃麵</t>
+          <t>一段深夜巷口的短影音，燈還亮著，有人坐在騎樓吃麵，熱氣一直冒</t>
         </is>
       </c>
       <c r="D3" s="29" t="inlineStr">
@@ -679,7 +679,7 @@
     <row r="4" ht="15.75" customHeight="1" s="28">
       <c r="C4" s="29" t="inlineStr">
         <is>
-          <t>一段沒有配樂的影片，只有風吹過稻田的聲音</t>
+          <t>一段沒有配樂的短影音，只有風吹過稻田的聲音</t>
         </is>
       </c>
       <c r="D4" s="29" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="5" ht="15.75" customHeight="1" s="28">
       <c r="C5" s="29" t="inlineStr">
         <is>
-          <t>一張步道上的照片，前一晚的雨還掛在葉尖上</t>
+          <t>一段步道的短影音，鏡頭掃過還掛著雨珠的葉子，水滴一顆顆往下落</t>
         </is>
       </c>
       <c r="D5" s="29" t="inlineStr">

--- a/data.xlsx
+++ b/data.xlsx
@@ -611,7 +611,7 @@
       </c>
       <c r="C2" s="29" t="inlineStr">
         <is>
-          <t>一段空拍退潮沙灘的短影音，浪一波波把沙紋刷過去</t>
+          <t>一段空拍退潮沙灘的影片，浪一波波把沙紋刷過去</t>
         </is>
       </c>
       <c r="D2" s="29" t="inlineStr">
@@ -645,7 +645,7 @@
     <row r="3" ht="15.75" customHeight="1" s="28">
       <c r="C3" s="29" t="inlineStr">
         <is>
-          <t>一段深夜巷口的短影音，燈還亮著，有人坐在騎樓吃麵，熱氣一直冒</t>
+          <t>一段深夜巷口的影片，燈還亮著，有人坐在騎樓吃麵，熱氣一直冒</t>
         </is>
       </c>
       <c r="D3" s="29" t="inlineStr">
@@ -679,7 +679,7 @@
     <row r="4" ht="15.75" customHeight="1" s="28">
       <c r="C4" s="29" t="inlineStr">
         <is>
-          <t>一段沒有配樂的短影音，只有風吹過稻田的聲音</t>
+          <t>一段沒有配樂的影片，只有風吹過稻田的聲音</t>
         </is>
       </c>
       <c r="D4" s="29" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="5" ht="15.75" customHeight="1" s="28">
       <c r="C5" s="29" t="inlineStr">
         <is>
-          <t>一段步道的短影音，鏡頭掃過還掛著雨珠的葉子，水滴一顆顆往下落</t>
+          <t>一段步道的影片，鏡頭掃過還掛著雨珠的葉子，水滴一顆顆往下落</t>
         </is>
       </c>
       <c r="D5" s="29" t="inlineStr">
